--- a/source/05_DeepLearning/data/heart-disease.xlsx
+++ b/source/05_DeepLearning/data/heart-disease.xlsx
@@ -1,20 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\big\src\09_ML_DL\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\source\05_DeepLearning\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C932A2-9983-4F50-9A83-BB1402E60811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27120" yWindow="2460" windowWidth="19356" windowHeight="17640"/>
+    <workbookView xWindow="2880" yWindow="645" windowWidth="25875" windowHeight="14250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="processed.cleveland" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -78,7 +90,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -626,9 +638,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -666,9 +678,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -703,7 +715,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -738,7 +750,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -911,11 +923,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N304"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R304"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -958,8 +970,9 @@
       <c r="N1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>63</v>
       </c>
@@ -1003,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>67</v>
       </c>
@@ -1047,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>67</v>
       </c>
@@ -1091,7 +1104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>37</v>
       </c>
@@ -1135,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>41</v>
       </c>
@@ -1179,7 +1192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>56</v>
       </c>
@@ -1223,7 +1236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>62</v>
       </c>
@@ -1267,7 +1280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>57</v>
       </c>
@@ -1311,7 +1324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>63</v>
       </c>
@@ -1355,7 +1368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>53</v>
       </c>
@@ -1399,7 +1412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>57</v>
       </c>
@@ -1443,7 +1456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>56</v>
       </c>
@@ -1487,7 +1500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>56</v>
       </c>
@@ -1531,7 +1544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>44</v>
       </c>
@@ -1575,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>52</v>
       </c>
@@ -1619,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>57</v>
       </c>
@@ -1663,7 +1676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>48</v>
       </c>
@@ -1707,7 +1720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>54</v>
       </c>
@@ -1751,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>48</v>
       </c>
@@ -1795,7 +1808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>49</v>
       </c>
@@ -1839,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>64</v>
       </c>
@@ -1883,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>58</v>
       </c>
@@ -1927,7 +1940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>58</v>
       </c>
@@ -1971,7 +1984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>58</v>
       </c>
@@ -2015,7 +2028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>60</v>
       </c>
@@ -2059,7 +2072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>50</v>
       </c>
@@ -2103,7 +2116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>58</v>
       </c>
@@ -2147,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>66</v>
       </c>
@@ -2191,7 +2204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>43</v>
       </c>
@@ -2235,7 +2248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>40</v>
       </c>
@@ -2279,7 +2292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>69</v>
       </c>
@@ -2323,7 +2336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>60</v>
       </c>
@@ -2367,7 +2380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>64</v>
       </c>
@@ -2411,7 +2424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>59</v>
       </c>
@@ -2455,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>44</v>
       </c>
@@ -2499,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>42</v>
       </c>
@@ -2543,7 +2556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>43</v>
       </c>
@@ -2587,7 +2600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>57</v>
       </c>
@@ -2631,7 +2644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>55</v>
       </c>
@@ -2675,7 +2688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>61</v>
       </c>
@@ -2719,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>65</v>
       </c>
@@ -2763,7 +2776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>40</v>
       </c>
@@ -2807,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>71</v>
       </c>
@@ -2851,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>59</v>
       </c>
@@ -2895,7 +2908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>61</v>
       </c>
@@ -2939,7 +2952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>58</v>
       </c>
@@ -2983,7 +2996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>51</v>
       </c>
@@ -3027,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>50</v>
       </c>
@@ -3071,7 +3084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>65</v>
       </c>
@@ -3115,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>53</v>
       </c>
@@ -3159,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>41</v>
       </c>
@@ -3203,7 +3216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>65</v>
       </c>
@@ -3247,7 +3260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>44</v>
       </c>
@@ -3291,7 +3304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>44</v>
       </c>
@@ -3335,7 +3348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>60</v>
       </c>
@@ -3379,7 +3392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>54</v>
       </c>
@@ -3423,7 +3436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>50</v>
       </c>
@@ -3467,7 +3480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>41</v>
       </c>
@@ -3511,7 +3524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>54</v>
       </c>
@@ -3555,7 +3568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>51</v>
       </c>
@@ -3599,7 +3612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>51</v>
       </c>
@@ -3643,7 +3656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>46</v>
       </c>
@@ -3687,7 +3700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>58</v>
       </c>
@@ -3731,7 +3744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>54</v>
       </c>
@@ -3775,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>54</v>
       </c>
@@ -3819,7 +3832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>60</v>
       </c>
@@ -3863,7 +3876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>60</v>
       </c>
@@ -3907,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>54</v>
       </c>
@@ -3951,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>59</v>
       </c>
@@ -3995,7 +4008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>46</v>
       </c>
@@ -4039,7 +4052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>65</v>
       </c>
@@ -4083,7 +4096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>67</v>
       </c>
@@ -4127,7 +4140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>62</v>
       </c>
@@ -4171,7 +4184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>65</v>
       </c>
@@ -4215,7 +4228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>44</v>
       </c>
@@ -4259,7 +4272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>65</v>
       </c>
@@ -4303,7 +4316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>60</v>
       </c>
@@ -4347,7 +4360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>51</v>
       </c>
@@ -4391,7 +4404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>48</v>
       </c>
@@ -4435,7 +4448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>58</v>
       </c>
@@ -4479,7 +4492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>45</v>
       </c>
@@ -4523,7 +4536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>53</v>
       </c>
@@ -4567,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>39</v>
       </c>
@@ -4611,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>68</v>
       </c>
@@ -4655,7 +4668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>52</v>
       </c>
@@ -4699,7 +4712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>44</v>
       </c>
@@ -4743,7 +4756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>47</v>
       </c>
@@ -4787,7 +4800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>53</v>
       </c>
@@ -4831,7 +4844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>53</v>
       </c>
@@ -4875,7 +4888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>51</v>
       </c>
@@ -4919,7 +4932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>66</v>
       </c>
@@ -4963,7 +4976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>62</v>
       </c>
@@ -5007,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>62</v>
       </c>
@@ -5051,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>44</v>
       </c>
@@ -5095,7 +5108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>63</v>
       </c>
@@ -5139,7 +5152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>52</v>
       </c>
@@ -5183,7 +5196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>59</v>
       </c>
@@ -5227,7 +5240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>60</v>
       </c>
@@ -5271,7 +5284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>52</v>
       </c>
@@ -5315,7 +5328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>48</v>
       </c>
@@ -5359,7 +5372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>45</v>
       </c>
@@ -5403,7 +5416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>34</v>
       </c>
@@ -5447,7 +5460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>57</v>
       </c>
@@ -5491,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>71</v>
       </c>
@@ -5535,7 +5548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>49</v>
       </c>
@@ -5579,7 +5592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>54</v>
       </c>
@@ -5623,7 +5636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>59</v>
       </c>
@@ -5667,7 +5680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>57</v>
       </c>
@@ -5711,7 +5724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>61</v>
       </c>
@@ -5755,7 +5768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>39</v>
       </c>
@@ -5799,7 +5812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>61</v>
       </c>
@@ -5843,7 +5856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>56</v>
       </c>
@@ -5887,7 +5900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>52</v>
       </c>
@@ -5931,7 +5944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>43</v>
       </c>
@@ -5975,7 +5988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>62</v>
       </c>
@@ -6019,7 +6032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>41</v>
       </c>
@@ -6063,7 +6076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>58</v>
       </c>
@@ -6107,7 +6120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>35</v>
       </c>
@@ -6151,7 +6164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>63</v>
       </c>
@@ -6195,7 +6208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>65</v>
       </c>
@@ -6239,7 +6252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>48</v>
       </c>
@@ -6283,7 +6296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>63</v>
       </c>
@@ -6327,7 +6340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>51</v>
       </c>
@@ -6371,7 +6384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>55</v>
       </c>
@@ -6415,7 +6428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>65</v>
       </c>
@@ -6459,7 +6472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>45</v>
       </c>
@@ -6503,7 +6516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>56</v>
       </c>
@@ -6547,7 +6560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>54</v>
       </c>
@@ -6591,7 +6604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>44</v>
       </c>
@@ -6635,7 +6648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>62</v>
       </c>
@@ -6679,7 +6692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>54</v>
       </c>
@@ -6723,7 +6736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>51</v>
       </c>
@@ -6767,7 +6780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>29</v>
       </c>
@@ -6811,7 +6824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>51</v>
       </c>
@@ -6855,7 +6868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>43</v>
       </c>
@@ -6899,7 +6912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>55</v>
       </c>
@@ -6943,7 +6956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>70</v>
       </c>
@@ -6987,7 +7000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>62</v>
       </c>
@@ -7031,7 +7044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>35</v>
       </c>
@@ -7075,7 +7088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>51</v>
       </c>
@@ -7119,7 +7132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>59</v>
       </c>
@@ -7163,7 +7176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>59</v>
       </c>
@@ -7207,7 +7220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>52</v>
       </c>
@@ -7251,7 +7264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>64</v>
       </c>
@@ -7295,7 +7308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>58</v>
       </c>
@@ -7339,7 +7352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>47</v>
       </c>
@@ -7383,7 +7396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>57</v>
       </c>
@@ -7427,7 +7440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>41</v>
       </c>
@@ -7471,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>45</v>
       </c>
@@ -7515,7 +7528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>60</v>
       </c>
@@ -7559,7 +7572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>52</v>
       </c>
@@ -7603,7 +7616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>42</v>
       </c>
@@ -7647,7 +7660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>67</v>
       </c>
@@ -7691,7 +7704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>55</v>
       </c>
@@ -7735,7 +7748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>64</v>
       </c>
@@ -7779,7 +7792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>70</v>
       </c>
@@ -7823,7 +7836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>51</v>
       </c>
@@ -7867,7 +7880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>58</v>
       </c>
@@ -7911,7 +7924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>60</v>
       </c>
@@ -7955,7 +7968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>68</v>
       </c>
@@ -7999,7 +8012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>46</v>
       </c>
@@ -8043,7 +8056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>77</v>
       </c>
@@ -8087,7 +8100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>54</v>
       </c>
@@ -8131,7 +8144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>58</v>
       </c>
@@ -8175,7 +8188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>48</v>
       </c>
@@ -8219,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>57</v>
       </c>
@@ -8263,7 +8276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>52</v>
       </c>
@@ -8307,7 +8320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>54</v>
       </c>
@@ -8351,7 +8364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>35</v>
       </c>
@@ -8395,7 +8408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>45</v>
       </c>
@@ -8439,7 +8452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>70</v>
       </c>
@@ -8483,7 +8496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>53</v>
       </c>
@@ -8527,7 +8540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>59</v>
       </c>
@@ -8571,7 +8584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>62</v>
       </c>
@@ -8615,7 +8628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>64</v>
       </c>
@@ -8659,7 +8672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>57</v>
       </c>
@@ -8703,7 +8716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>52</v>
       </c>
@@ -8747,7 +8760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>56</v>
       </c>
@@ -8791,7 +8804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>43</v>
       </c>
@@ -8835,7 +8848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>53</v>
       </c>
@@ -8879,7 +8892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>48</v>
       </c>
@@ -8923,7 +8936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>56</v>
       </c>
@@ -8967,7 +8980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>42</v>
       </c>
@@ -9011,7 +9024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>59</v>
       </c>
@@ -9055,7 +9068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>60</v>
       </c>
@@ -9099,7 +9112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>63</v>
       </c>
@@ -9143,7 +9156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>42</v>
       </c>
@@ -9187,7 +9200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>66</v>
       </c>
@@ -9231,7 +9244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>54</v>
       </c>
@@ -9275,7 +9288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>69</v>
       </c>
@@ -9319,7 +9332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>50</v>
       </c>
@@ -9363,7 +9376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>51</v>
       </c>
@@ -9407,7 +9420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>43</v>
       </c>
@@ -9451,7 +9464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>62</v>
       </c>
@@ -9495,7 +9508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>68</v>
       </c>
@@ -9539,7 +9552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>67</v>
       </c>
@@ -9583,7 +9596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>69</v>
       </c>
@@ -9627,7 +9640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>45</v>
       </c>
@@ -9671,7 +9684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>50</v>
       </c>
@@ -9715,7 +9728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>59</v>
       </c>
@@ -9759,7 +9772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>50</v>
       </c>
@@ -9803,7 +9816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>64</v>
       </c>
@@ -9847,7 +9860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>57</v>
       </c>
@@ -9891,7 +9904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>64</v>
       </c>
@@ -9935,7 +9948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>43</v>
       </c>
@@ -9979,7 +9992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>45</v>
       </c>
@@ -10023,7 +10036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>58</v>
       </c>
@@ -10067,7 +10080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>50</v>
       </c>
@@ -10111,7 +10124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>55</v>
       </c>
@@ -10155,7 +10168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>62</v>
       </c>
@@ -10199,7 +10212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>37</v>
       </c>
@@ -10243,7 +10256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>38</v>
       </c>
@@ -10287,7 +10300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>41</v>
       </c>
@@ -10331,7 +10344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>66</v>
       </c>
@@ -10375,7 +10388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>52</v>
       </c>
@@ -10419,7 +10432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>56</v>
       </c>
@@ -10463,7 +10476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>46</v>
       </c>
@@ -10507,7 +10520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>46</v>
       </c>
@@ -10551,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>64</v>
       </c>
@@ -10595,7 +10608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>59</v>
       </c>
@@ -10639,7 +10652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>41</v>
       </c>
@@ -10683,7 +10696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>54</v>
       </c>
@@ -10727,7 +10740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>39</v>
       </c>
@@ -10771,7 +10784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>53</v>
       </c>
@@ -10815,7 +10828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>63</v>
       </c>
@@ -10859,7 +10872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>34</v>
       </c>
@@ -10903,7 +10916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>47</v>
       </c>
@@ -10947,7 +10960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>67</v>
       </c>
@@ -10991,7 +11004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>54</v>
       </c>
@@ -11035,7 +11048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>66</v>
       </c>
@@ -11079,7 +11092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>52</v>
       </c>
@@ -11123,7 +11136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>55</v>
       </c>
@@ -11167,7 +11180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>49</v>
       </c>
@@ -11211,7 +11224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>74</v>
       </c>
@@ -11255,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>54</v>
       </c>
@@ -11299,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>54</v>
       </c>
@@ -11343,7 +11356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>56</v>
       </c>
@@ -11387,7 +11400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>46</v>
       </c>
@@ -11431,7 +11444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>49</v>
       </c>
@@ -11475,7 +11488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>42</v>
       </c>
@@ -11519,7 +11532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>41</v>
       </c>
@@ -11563,7 +11576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>41</v>
       </c>
@@ -11607,7 +11620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>49</v>
       </c>
@@ -11651,7 +11664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>61</v>
       </c>
@@ -11695,7 +11708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>60</v>
       </c>
@@ -11739,7 +11752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>67</v>
       </c>
@@ -11783,7 +11796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>58</v>
       </c>
@@ -11827,7 +11840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>47</v>
       </c>
@@ -11871,7 +11884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>52</v>
       </c>
@@ -11915,7 +11928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>62</v>
       </c>
@@ -11959,7 +11972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>57</v>
       </c>
@@ -12003,7 +12016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>58</v>
       </c>
@@ -12047,7 +12060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>64</v>
       </c>
@@ -12091,7 +12104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>51</v>
       </c>
@@ -12135,7 +12148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>43</v>
       </c>
@@ -12179,7 +12192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>42</v>
       </c>
@@ -12223,7 +12236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>67</v>
       </c>
@@ -12267,7 +12280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>76</v>
       </c>
@@ -12311,7 +12324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>70</v>
       </c>
@@ -12355,7 +12368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>57</v>
       </c>
@@ -12399,7 +12412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>44</v>
       </c>
@@ -12443,7 +12456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>58</v>
       </c>
@@ -12487,7 +12500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>60</v>
       </c>
@@ -12531,7 +12544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>44</v>
       </c>
@@ -12575,7 +12588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>61</v>
       </c>
@@ -12619,7 +12632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>42</v>
       </c>
@@ -12663,7 +12676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>52</v>
       </c>
@@ -12707,7 +12720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>59</v>
       </c>
@@ -12751,7 +12764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>40</v>
       </c>
@@ -12795,7 +12808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>42</v>
       </c>
@@ -12839,7 +12852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>61</v>
       </c>
@@ -12883,7 +12896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>66</v>
       </c>
@@ -12927,7 +12940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>46</v>
       </c>
@@ -12971,7 +12984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>71</v>
       </c>
@@ -13015,7 +13028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>59</v>
       </c>
@@ -13059,7 +13072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>64</v>
       </c>
@@ -13103,7 +13116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>66</v>
       </c>
@@ -13147,7 +13160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>39</v>
       </c>
@@ -13191,7 +13204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>57</v>
       </c>
@@ -13235,7 +13248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>58</v>
       </c>
@@ -13279,7 +13292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>57</v>
       </c>
@@ -13323,7 +13336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>47</v>
       </c>
@@ -13367,7 +13380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>55</v>
       </c>
@@ -13411,7 +13424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>35</v>
       </c>
@@ -13455,7 +13468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>61</v>
       </c>
@@ -13499,7 +13512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>58</v>
       </c>
@@ -13543,7 +13556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>58</v>
       </c>
@@ -13587,7 +13600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>58</v>
       </c>
@@ -13631,7 +13644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>56</v>
       </c>
@@ -13675,7 +13688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>56</v>
       </c>
@@ -13719,7 +13732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>67</v>
       </c>
@@ -13763,7 +13776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>55</v>
       </c>
@@ -13807,7 +13820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>44</v>
       </c>
@@ -13851,7 +13864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>63</v>
       </c>
@@ -13895,7 +13908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>63</v>
       </c>
@@ -13939,7 +13952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>41</v>
       </c>
@@ -13983,7 +13996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>59</v>
       </c>
@@ -14027,7 +14040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>57</v>
       </c>
@@ -14071,7 +14084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>45</v>
       </c>
@@ -14115,7 +14128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>68</v>
       </c>
@@ -14159,7 +14172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>57</v>
       </c>
@@ -14203,7 +14216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>57</v>
       </c>
@@ -14247,7 +14260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>38</v>
       </c>
